--- a/sample_data/AWS_Transform_Kiro.xlsx
+++ b/sample_data/AWS_Transform_Kiro.xlsx
@@ -282,7 +282,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -296,11 +296,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -431,6 +459,8 @@
     <xf numFmtId="0" fontId="34" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -509,7 +539,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -645,7 +674,6 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -770,7 +798,6 @@
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -833,7 +860,6 @@
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -961,7 +987,6 @@
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -1089,7 +1114,6 @@
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -1226,7 +1250,6 @@
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -1356,7 +1379,6 @@
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -3447,21 +3469,21 @@
           <t>Phase 1: Discovery &amp; Assessment [COMPLETED]</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n"/>
-      <c r="C6" s="10" t="n"/>
-      <c r="D6" s="10" t="n"/>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n"/>
-      <c r="I6" s="10" t="n"/>
-      <c r="J6" s="10" t="n"/>
-      <c r="K6" s="10" t="n"/>
-      <c r="L6" s="10" t="n"/>
-      <c r="M6" s="10" t="n"/>
-      <c r="N6" s="10" t="n"/>
-      <c r="O6" s="10" t="n"/>
-      <c r="P6" s="10" t="n"/>
+      <c r="B6" s="96" t="n"/>
+      <c r="C6" s="96" t="n"/>
+      <c r="D6" s="96" t="n"/>
+      <c r="E6" s="96" t="n"/>
+      <c r="F6" s="96" t="n"/>
+      <c r="G6" s="96" t="n"/>
+      <c r="H6" s="96" t="n"/>
+      <c r="I6" s="96" t="n"/>
+      <c r="J6" s="96" t="n"/>
+      <c r="K6" s="96" t="n"/>
+      <c r="L6" s="96" t="n"/>
+      <c r="M6" s="96" t="n"/>
+      <c r="N6" s="96" t="n"/>
+      <c r="O6" s="96" t="n"/>
+      <c r="P6" s="97" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -4099,21 +4121,21 @@
           <t>Phase 2: Planning &amp; Design</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
-      <c r="F17" s="10" t="n"/>
-      <c r="G17" s="10" t="n"/>
-      <c r="H17" s="10" t="n"/>
-      <c r="I17" s="10" t="n"/>
-      <c r="J17" s="10" t="n"/>
-      <c r="K17" s="10" t="n"/>
-      <c r="L17" s="10" t="n"/>
-      <c r="M17" s="10" t="n"/>
-      <c r="N17" s="10" t="n"/>
-      <c r="O17" s="10" t="n"/>
-      <c r="P17" s="10" t="n"/>
+      <c r="B17" s="96" t="n"/>
+      <c r="C17" s="96" t="n"/>
+      <c r="D17" s="96" t="n"/>
+      <c r="E17" s="96" t="n"/>
+      <c r="F17" s="96" t="n"/>
+      <c r="G17" s="96" t="n"/>
+      <c r="H17" s="96" t="n"/>
+      <c r="I17" s="96" t="n"/>
+      <c r="J17" s="96" t="n"/>
+      <c r="K17" s="96" t="n"/>
+      <c r="L17" s="96" t="n"/>
+      <c r="M17" s="96" t="n"/>
+      <c r="N17" s="96" t="n"/>
+      <c r="O17" s="96" t="n"/>
+      <c r="P17" s="97" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
@@ -4709,21 +4731,21 @@
           <t>Phase 3: Build &amp; Prepare</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
-      <c r="D27" s="10" t="n"/>
-      <c r="E27" s="10" t="n"/>
-      <c r="F27" s="10" t="n"/>
-      <c r="G27" s="10" t="n"/>
-      <c r="H27" s="10" t="n"/>
-      <c r="I27" s="10" t="n"/>
-      <c r="J27" s="10" t="n"/>
-      <c r="K27" s="10" t="n"/>
-      <c r="L27" s="10" t="n"/>
-      <c r="M27" s="10" t="n"/>
-      <c r="N27" s="10" t="n"/>
-      <c r="O27" s="10" t="n"/>
-      <c r="P27" s="10" t="n"/>
+      <c r="B27" s="96" t="n"/>
+      <c r="C27" s="96" t="n"/>
+      <c r="D27" s="96" t="n"/>
+      <c r="E27" s="96" t="n"/>
+      <c r="F27" s="96" t="n"/>
+      <c r="G27" s="96" t="n"/>
+      <c r="H27" s="96" t="n"/>
+      <c r="I27" s="96" t="n"/>
+      <c r="J27" s="96" t="n"/>
+      <c r="K27" s="96" t="n"/>
+      <c r="L27" s="96" t="n"/>
+      <c r="M27" s="96" t="n"/>
+      <c r="N27" s="96" t="n"/>
+      <c r="O27" s="96" t="n"/>
+      <c r="P27" s="97" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -5451,21 +5473,21 @@
           <t>Phase 4: Migration Execution</t>
         </is>
       </c>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="10" t="n"/>
-      <c r="D39" s="10" t="n"/>
-      <c r="E39" s="10" t="n"/>
-      <c r="F39" s="10" t="n"/>
-      <c r="G39" s="10" t="n"/>
-      <c r="H39" s="10" t="n"/>
-      <c r="I39" s="10" t="n"/>
-      <c r="J39" s="10" t="n"/>
-      <c r="K39" s="10" t="n"/>
-      <c r="L39" s="10" t="n"/>
-      <c r="M39" s="10" t="n"/>
-      <c r="N39" s="10" t="n"/>
-      <c r="O39" s="10" t="n"/>
-      <c r="P39" s="10" t="n"/>
+      <c r="B39" s="96" t="n"/>
+      <c r="C39" s="96" t="n"/>
+      <c r="D39" s="96" t="n"/>
+      <c r="E39" s="96" t="n"/>
+      <c r="F39" s="96" t="n"/>
+      <c r="G39" s="96" t="n"/>
+      <c r="H39" s="96" t="n"/>
+      <c r="I39" s="96" t="n"/>
+      <c r="J39" s="96" t="n"/>
+      <c r="K39" s="96" t="n"/>
+      <c r="L39" s="96" t="n"/>
+      <c r="M39" s="96" t="n"/>
+      <c r="N39" s="96" t="n"/>
+      <c r="O39" s="96" t="n"/>
+      <c r="P39" s="97" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
@@ -6199,21 +6221,21 @@
           <t>Phase 4a: Testing (IQE-Led)</t>
         </is>
       </c>
-      <c r="B51" s="10" t="n"/>
-      <c r="C51" s="10" t="n"/>
-      <c r="D51" s="10" t="n"/>
-      <c r="E51" s="10" t="n"/>
-      <c r="F51" s="10" t="n"/>
-      <c r="G51" s="10" t="n"/>
-      <c r="H51" s="10" t="n"/>
-      <c r="I51" s="10" t="n"/>
-      <c r="J51" s="10" t="n"/>
-      <c r="K51" s="10" t="n"/>
-      <c r="L51" s="10" t="n"/>
-      <c r="M51" s="10" t="n"/>
-      <c r="N51" s="10" t="n"/>
-      <c r="O51" s="10" t="n"/>
-      <c r="P51" s="10" t="n"/>
+      <c r="B51" s="96" t="n"/>
+      <c r="C51" s="96" t="n"/>
+      <c r="D51" s="96" t="n"/>
+      <c r="E51" s="96" t="n"/>
+      <c r="F51" s="96" t="n"/>
+      <c r="G51" s="96" t="n"/>
+      <c r="H51" s="96" t="n"/>
+      <c r="I51" s="96" t="n"/>
+      <c r="J51" s="96" t="n"/>
+      <c r="K51" s="96" t="n"/>
+      <c r="L51" s="96" t="n"/>
+      <c r="M51" s="96" t="n"/>
+      <c r="N51" s="96" t="n"/>
+      <c r="O51" s="96" t="n"/>
+      <c r="P51" s="97" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n"/>
@@ -6617,21 +6639,21 @@
           <t>Phase 5: Post-Migration Optimize</t>
         </is>
       </c>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="10" t="n"/>
-      <c r="E58" s="10" t="n"/>
-      <c r="F58" s="10" t="n"/>
-      <c r="G58" s="10" t="n"/>
-      <c r="H58" s="10" t="n"/>
-      <c r="I58" s="10" t="n"/>
-      <c r="J58" s="10" t="n"/>
-      <c r="K58" s="10" t="n"/>
-      <c r="L58" s="10" t="n"/>
-      <c r="M58" s="10" t="n"/>
-      <c r="N58" s="10" t="n"/>
-      <c r="O58" s="10" t="n"/>
-      <c r="P58" s="10" t="n"/>
+      <c r="B58" s="96" t="n"/>
+      <c r="C58" s="96" t="n"/>
+      <c r="D58" s="96" t="n"/>
+      <c r="E58" s="96" t="n"/>
+      <c r="F58" s="96" t="n"/>
+      <c r="G58" s="96" t="n"/>
+      <c r="H58" s="96" t="n"/>
+      <c r="I58" s="96" t="n"/>
+      <c r="J58" s="96" t="n"/>
+      <c r="K58" s="96" t="n"/>
+      <c r="L58" s="96" t="n"/>
+      <c r="M58" s="96" t="n"/>
+      <c r="N58" s="96" t="n"/>
+      <c r="O58" s="96" t="n"/>
+      <c r="P58" s="97" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -8327,6 +8349,8 @@
       </c>
       <c r="I29" s="15" t="n"/>
     </row>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
@@ -8462,7 +8486,7 @@
         <v>68</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>14</v>
@@ -8509,7 +8533,7 @@
         <v>108</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>18</v>
@@ -8556,7 +8580,7 @@
         <v>83</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E37" s="7" t="n">
         <v>14</v>
@@ -8650,7 +8674,7 @@
         <v>30</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>8</v>
@@ -8697,7 +8721,7 @@
         <v>53</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E40" s="7" t="n">
         <v>9</v>
@@ -8744,7 +8768,7 @@
         <v>32</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>6</v>
@@ -8791,7 +8815,7 @@
         <v>20</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E42" s="7" t="n">
         <v>5</v>
@@ -8838,7 +8862,7 @@
         <v>68</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>4</v>
@@ -8959,6 +8983,8 @@
         <v/>
       </c>
     </row>
+    <row r="46"/>
+    <row r="47"/>
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>
@@ -9413,6 +9439,7 @@
   <sheetPr>
     <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:R60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>

--- a/sample_data/AWS_Transform_Kiro.xlsx
+++ b/sample_data/AWS_Transform_Kiro.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Dashboard" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team Revenue View" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tool vs Industry Benchmark" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cost by Cloud" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,7 +30,7 @@
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="+0%;-0%"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="39">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -207,6 +208,19 @@
     <font>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -328,7 +342,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -461,6 +475,15 @@
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="31" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="37" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -8349,8 +8372,6 @@
       </c>
       <c r="I29" s="15" t="n"/>
     </row>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
@@ -8983,8 +9004,6 @@
         <v/>
       </c>
     </row>
-    <row r="46"/>
-    <row r="47"/>
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>
@@ -12410,4 +12429,505 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002E75B6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>PG&amp;E Migration Cost by Cloud Platform — AWS Transform+Kiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>415 Apps | 4,273 Servers | Discovery COMPLETED | PG&amp;E provides LZ/Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>Section A: Migration Duration by Cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Cloud Platform</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Apps</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Servers</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Traditional
+Days</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>AI Factor</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>AI Days</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Days Saved</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Savings %</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Months
+Saved</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="98" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>107</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>719</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>533</v>
+      </c>
+      <c r="E6" s="79" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F6" s="5">
+        <f>D6*E6</f>
+        <v/>
+      </c>
+      <c r="G6" s="5">
+        <f>D6-F6</f>
+        <v/>
+      </c>
+      <c r="H6" s="79">
+        <f>IF(D6&gt;0,(D6-F6)/D6,0)</f>
+        <v/>
+      </c>
+      <c r="I6" s="5">
+        <f>ROUND(G6/22,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="99" t="inlineStr">
+        <is>
+          <t>Azure</t>
+        </is>
+      </c>
+      <c r="B7" s="100" t="n">
+        <v>145</v>
+      </c>
+      <c r="C7" s="100" t="n">
+        <v>852</v>
+      </c>
+      <c r="D7" s="100" t="n">
+        <v>538</v>
+      </c>
+      <c r="E7" s="101" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F7" s="100">
+        <f>D7*E7</f>
+        <v/>
+      </c>
+      <c r="G7" s="100">
+        <f>D7-F7</f>
+        <v/>
+      </c>
+      <c r="H7" s="101">
+        <f>IF(D7&gt;0,(D7-F7)/D7,0)</f>
+        <v/>
+      </c>
+      <c r="I7" s="100">
+        <f>ROUND(G7/22,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="99" t="inlineStr">
+        <is>
+          <t>Azure Local / HyperV</t>
+        </is>
+      </c>
+      <c r="B8" s="100" t="n">
+        <v>130</v>
+      </c>
+      <c r="C8" s="100" t="n">
+        <v>2702</v>
+      </c>
+      <c r="D8" s="100" t="n">
+        <v>586</v>
+      </c>
+      <c r="E8" s="101" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="F8" s="100">
+        <f>D8*E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="100">
+        <f>D8-F8</f>
+        <v/>
+      </c>
+      <c r="H8" s="101">
+        <f>IF(D8&gt;0,(D8-F8)/D8,0)</f>
+        <v/>
+      </c>
+      <c r="I8" s="100">
+        <f>ROUND(G8/22,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B9" s="15">
+        <f>SUM(B6:B8)</f>
+        <v/>
+      </c>
+      <c r="C9" s="15">
+        <f>SUM(C6:C8)</f>
+        <v/>
+      </c>
+      <c r="D9" s="15">
+        <f>SUM(D6:D8)</f>
+        <v/>
+      </c>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="15">
+        <f>SUM(F6:F8)</f>
+        <v/>
+      </c>
+      <c r="G9" s="15">
+        <f>SUM(G6:G8)</f>
+        <v/>
+      </c>
+      <c r="H9" s="87">
+        <f>IF(D9&gt;0,(D9-F9)/D9,0)</f>
+        <v/>
+      </c>
+      <c r="I9" s="15">
+        <f>ROUND(G9/22,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>Section B: Migration Cost by Cloud (2-Year)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Cloud Platform</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>AI Days</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Avg FTEs</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Blended
+Rate ($)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Y1 Labor ($)</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Y2 Labor
+(13% SS)</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Platform
+License ($)</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Tooling &amp;
+Other ($)</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>2-Year Total ($)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="98" t="inlineStr">
+        <is>
+          <t>AWS (107 apps)</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>181</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" s="22" t="n">
+        <v>1050</v>
+      </c>
+      <c r="E14" s="22">
+        <f>B14*C14*D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="22">
+        <f>E14*0.13</f>
+        <v/>
+      </c>
+      <c r="G14" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="22" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I14" s="22">
+        <f>E14+F14+G14+H14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="99" t="inlineStr">
+        <is>
+          <t>Azure (145 apps)</t>
+        </is>
+      </c>
+      <c r="B15" s="100" t="n">
+        <v>269</v>
+      </c>
+      <c r="C15" s="100" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" s="102" t="n">
+        <v>1050</v>
+      </c>
+      <c r="E15" s="102">
+        <f>B15*C15*D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="102">
+        <f>E15*0.13</f>
+        <v/>
+      </c>
+      <c r="G15" s="102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="102" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I15" s="102">
+        <f>E15+F15+G15+H15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="99" t="inlineStr">
+        <is>
+          <t>Azure Local/HV (130 apps)</t>
+        </is>
+      </c>
+      <c r="B16" s="100" t="n">
+        <v>305</v>
+      </c>
+      <c r="C16" s="100" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" s="102" t="n">
+        <v>1050</v>
+      </c>
+      <c r="E16" s="102">
+        <f>B16*C16*D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="102">
+        <f>E16*0.13</f>
+        <v/>
+      </c>
+      <c r="G16" s="102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="102" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I16" s="102">
+        <f>E16+F16+G16+H16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Contingency (12%)</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="22">
+        <f>SUM(I14:I16)*0.12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>GRAND TOTAL (2-Year)</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="23">
+        <f>SUM(E14:E16)</f>
+        <v/>
+      </c>
+      <c r="F18" s="23">
+        <f>SUM(F14:F16)</f>
+        <v/>
+      </c>
+      <c r="G18" s="15" t="n"/>
+      <c r="H18" s="15" t="n"/>
+      <c r="I18" s="23">
+        <f>SUM(I14:I16)+I17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="86" t="inlineStr">
+        <is>
+          <t>Traditional 2-Year (No AI)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="103" t="n">
+        <v>12349312.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="77" t="inlineStr">
+        <is>
+          <t>NET SAVINGS</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="104">
+        <f>I20-I18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>Tool: AWS Transform+Kiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="105" t="inlineStr">
+        <is>
+          <t>AWS-native: best for AWS. Azure/AzLocal use industry-std tools (50-52%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="106" t="inlineStr">
+        <is>
+          <t>CAVEAT: Yellow rows = Azure/AzLocal use industry-standard tools (50-52% savings), NOT AWS-native tools</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/sample_data/AWS_Transform_Kiro.xlsx
+++ b/sample_data/AWS_Transform_Kiro.xlsx
@@ -8372,6 +8372,8 @@
       </c>
       <c r="I29" s="15" t="n"/>
     </row>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
@@ -8504,13 +8506,13 @@
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F35" s="21" t="n">
         <v>1100</v>
@@ -8551,13 +8553,13 @@
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F36" s="21" t="n">
         <v>1050</v>
@@ -8598,13 +8600,13 @@
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F37" s="21" t="n">
         <v>1050</v>
@@ -8645,13 +8647,13 @@
         </is>
       </c>
       <c r="C38" s="7" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F38" s="21" t="n">
         <v>1000</v>
@@ -8692,13 +8694,13 @@
         </is>
       </c>
       <c r="C39" s="7" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D39" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="E39" s="7" t="n">
         <v>10</v>
-      </c>
-      <c r="E39" s="7" t="n">
-        <v>8</v>
       </c>
       <c r="F39" s="21" t="n">
         <v>1100</v>
@@ -8739,13 +8741,13 @@
         </is>
       </c>
       <c r="C40" s="7" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F40" s="21" t="n">
         <v>1000</v>
@@ -8786,13 +8788,13 @@
         </is>
       </c>
       <c r="C41" s="7" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F41" s="21" t="n">
         <v>1050</v>
@@ -8833,13 +8835,13 @@
         </is>
       </c>
       <c r="C42" s="7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D42" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" s="7" t="n">
         <v>7</v>
-      </c>
-      <c r="E42" s="7" t="n">
-        <v>5</v>
       </c>
       <c r="F42" s="21" t="n">
         <v>1100</v>
@@ -8880,13 +8882,13 @@
         </is>
       </c>
       <c r="C43" s="7" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F43" s="21" t="n">
         <v>1100</v>
@@ -8927,13 +8929,13 @@
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F44" s="21" t="n">
         <v>1050</v>
@@ -9004,6 +9006,8 @@
         <v/>
       </c>
     </row>
+    <row r="46"/>
+    <row r="47"/>
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>

--- a/sample_data/AWS_Transform_Kiro.xlsx
+++ b/sample_data/AWS_Transform_Kiro.xlsx
@@ -8506,10 +8506,10 @@
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>16</v>
@@ -8553,10 +8553,10 @@
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>53</v>
+        <v>143</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>22</v>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>41</v>
+        <v>117</v>
       </c>
       <c r="E37" s="7" t="n">
         <v>16</v>
@@ -8647,10 +8647,10 @@
         </is>
       </c>
       <c r="C38" s="7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>17</v>
@@ -8697,7 +8697,7 @@
         <v>33</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>10</v>
@@ -8741,10 +8741,10 @@
         </is>
       </c>
       <c r="C40" s="7" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="E40" s="7" t="n">
         <v>11</v>
@@ -8791,7 +8791,7 @@
         <v>35</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>8</v>
@@ -8835,10 +8835,10 @@
         </is>
       </c>
       <c r="C42" s="7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E42" s="7" t="n">
         <v>7</v>
@@ -8882,10 +8882,10 @@
         </is>
       </c>
       <c r="C43" s="7" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>6</v>
@@ -8929,10 +8929,10 @@
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="E44" s="7" t="n">
         <v>10</v>
@@ -12735,7 +12735,7 @@
         <v>181</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D14" s="22" t="n">
         <v>1050</v>
@@ -12769,7 +12769,7 @@
         <v>269</v>
       </c>
       <c r="C15" s="100" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D15" s="102" t="n">
         <v>1050</v>
@@ -12803,7 +12803,7 @@
         <v>305</v>
       </c>
       <c r="C16" s="100" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D16" s="102" t="n">
         <v>1050</v>
@@ -12883,7 +12883,7 @@
       <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="n"/>
       <c r="I20" s="103" t="n">
-        <v>12349312.5</v>
+        <v>10840125</v>
       </c>
     </row>
     <row r="21">

--- a/sample_data/AWS_Transform_Kiro.xlsx
+++ b/sample_data/AWS_Transform_Kiro.xlsx
@@ -2084,11 +2084,11 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.3</v>
+        <v>0.37</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>68% savings. AWS Native auto-discovery is mature (agentless + agent-based), covers VMware/Hyper-V/physical well. Lacks unified multi-cloud single-pane — separate scans per platform need manual merging. [Ref: Gartner MQ 2024 + AWS Native product benchmark]</t>
+          <t>63% savings (WEIGHTED: AWS-native 70% x 26% + Industry 60% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -2114,11 +2114,11 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.35</v>
+        <v>0.42</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>62% savings. AWS Native dependency mapping uses network flow + process-level analysis. Good for standard dependencies but limited AI-augmented pattern detection for complex cross-app chains. [Ref: Gartner 2024 - AWS Native rated strong in discovery]</t>
+          <t>58% savings (WEIGHTED: AWS-native 65% x 26% + Industry 55% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -2144,11 +2144,11 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.28</v>
+        <v>0.37</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>65% savings. AWS Native integrates with AWS SCT/Azure DMA for schema analysis. Standard tool integration — no additional AI-assisted fix layer beyond what SCT provides. [Ref: AWS SCT docs + AWS Native integration docs]</t>
+          <t>63% savings (WEIGHTED: AWS-native 72% x 26% + Industry 60% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -2174,11 +2174,11 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>70% savings. AWS Native collects performance metrics via APIs — similar to industry standard. CloudWatch/Azure Monitor integration is well-implemented. [Ref: AWS CloudWatch + AWS Native perf module]</t>
+          <t>68% savings (WEIGHTED: AWS-native 75% x 26% + Industry 65% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -2204,11 +2204,11 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.42</v>
+        <v>0.49</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>50% savings. AWS Native has basic compliance checking but no dedicated compliance microservice. NERC CIP evidence collection is largely manual regardless of tool. [Ref: NERC CIP requirements + AWS Native docs]</t>
+          <t>51% savings (WEIGHTED: AWS-native 58% x 26% + Industry 48% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -2234,11 +2234,11 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.35</v>
+        <v>0.42</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>58% savings. AWS Native has license tracking module but limited AI-driven BYOL eligibility analysis. Standard CMDB-driven approach. [Ref: Flexera 2024 + AWS Native license module]</t>
+          <t>58% savings (WEIGHTED: AWS-native 65% x 26% + Industry 55% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -2264,11 +2264,11 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>70% savings. AWS Native has solid TCO modeling with cloud pricing integration. Covers AWS + Azure but requires separate runs per cloud — no single multi-cloud comparison view. [Ref: AWS Pricing + AWS Native cost module]</t>
+          <t>67% savings (WEIGHTED: AWS-native 72% x 26% + Industry 65% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -2294,11 +2294,11 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>62% savings. AWS Native wave planning uses dependency data + configurable rules. Functional but rule-based rather than AI-optimized — adequate for most scenarios. [Ref: McKinsey 2023 + AWS Native wave planner]</t>
+          <t>60% savings (WEIGHTED: AWS-native 65% x 26% + Industry 58% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -2324,11 +2324,11 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.3</v>
+        <v>0.37</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>65% savings (validation only — PG&amp;E provides LZ). AWS Native has LZ templates but limited auto-validation capability. [Ref: AWS Landing Zone Accelerator + AWS Native docs]</t>
+          <t>63% savings (WEIGHTED: AWS-native 70% x 26% + Industry 60% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -2354,11 +2354,11 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>70% savings. AWS Native generates Terraform/CloudFormation templates from discovery. Good template library but less dynamic auto-population from live inventory vs purpose-built IaC generators. [Ref: HashiCorp 2024 + AWS Native IaC module]</t>
+          <t>62% savings (WEIGHTED: AWS-native 68% x 26% + Industry 60% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -2384,11 +2384,11 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0.3</v>
+        <v>0.41</v>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>55% savings (Industry std: 60%). AWS Native has limited containerization support — basic Dockerfile templates but no AI source-code analysis for runtime dependency detection. Containerization is not AWS Native core strength. [Ref: CNCF 2024 + AWS Native product scope]</t>
+          <t>59% savings (WEIGHTED: AWS-native 70% x 26% + Industry 55% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -2414,11 +2414,11 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>42% savings. AWS Native does not provide framework upgrade assistance — this is outside AWS Native platform scope. Standard developer tooling (IDE + Copilot) applies. [Ref: AWS Native product scope — migration automation, not code modernization]</t>
+          <t>50% savings (WEIGHTED: AWS-native 65% x 26% + Industry 45% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -2444,11 +2444,11 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>42% savings. AWS Native has limited middleware migration support — basic config export for common middleware but no deep plugin compatibility analysis. [Ref: AWS Native product scope]</t>
+          <t>48% savings (WEIGHTED: AWS-native 55% x 26% + Industry 45% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -2474,11 +2474,11 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>60% savings. AWS Native wraps standard SCT/DMA — no additional AI-assisted fix layer. Complex stored proc conversion remains fully manual DBA work. [Ref: AWS SCT tiers + AWS Native DB module]</t>
+          <t>61% savings (WEIGHTED: AWS-native 70% x 26% + Industry 58% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -2504,11 +2504,11 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>57% savings. AWS Native has workflow-based rehearsal execution. Good orchestration but limited automated outcome validation — manual checklist-based verification. [Ref: AWS Native execution module]</t>
+          <t>54% savings (WEIGHTED: AWS-native 60% x 26% + Industry 52% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -2534,11 +2534,11 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>0.28</v>
+        <v>0.38</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>62% savings. AWS Native core strength — excellent rehost automation with MGN/ASR orchestration. Cutover workflow well-integrated. One of AWS Native best features. [Ref: AWS MGN + Gartner + AWS Native rehost module]</t>
+          <t>62% savings (WEIGHTED: AWS-native 72% x 26% + Industry 58% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -2564,11 +2564,11 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>0.38</v>
+        <v>0.45</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>55% savings. AWS Native supports basic replatform workflows (OS upgrade scripts) but less automated pre/post validation than purpose-built platforms. [Ref: Industry avg + AWS Native replatform module]</t>
+          <t>55% savings (WEIGHTED: AWS-native 62% x 26% + Industry 52% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -2594,11 +2594,11 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>52% savings. AWS Native has limited native containerization execution — relies on external CI/CD (Jenkins/GitHub Actions). No pre-configured pipeline from artifact generation. [Ref: CNCF 2024 + AWS Native product scope]</t>
+          <t>55% savings (WEIGHTED: AWS-native 65% x 26% + Industry 52% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -2624,11 +2624,11 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>0.48</v>
+        <v>0.53</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>45% savings. AWS Native has no native test generation capability. Testing relies on external test automation frameworks (Selenium, Cypress). No AI-assisted test case generation. [Ref: Forrester TEI + AWS Native product scope]</t>
+          <t>47% savings (WEIGHTED: AWS-native 52% x 26% + Industry 45% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -2654,11 +2654,11 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>47% savings. AWS Native has no performance test generation. Relies on external JMeter/Gatling. No auto-generated load scripts from traffic patterns. [Ref: Gartner + AWS Native product scope]</t>
+          <t>46% savings (WEIGHTED: AWS-native 48% x 26% + Industry 45% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -2684,11 +2684,11 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>70% savings. AWS Native integrates with cloud-native right-sizing tools (Compute Optimizer, Azure Advisor). Similar to industry standard — adds management layer. [Ref: AWS Compute Optimizer + AWS Native optimization module]</t>
+          <t>71% savings (WEIGHTED: AWS-native 78% x 26% + Industry 68% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -2714,11 +2714,11 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>0.3</v>
+        <v>0.41</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>55% savings. AWS Native has basic monitoring template deployment but limited auto-generation from discovery metadata. Standard CloudWatch/Azure Monitor setup required. [Ref: Datadog/Grafana + AWS Native docs]</t>
+          <t>59% savings (WEIGHTED: AWS-native 70% x 26% + Industry 55% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -2744,11 +2744,11 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>62% savings. AWS Native is not a vulnerability management platform — requires separate Nessus/Qualys integration. No migration-context-aware CVSS triage. [Ref: Tenable/Qualys + AWS Native product scope]</t>
+          <t>62% savings (WEIGHTED: AWS-native 67% x 26% + Industry 60% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -2774,11 +2774,11 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>52% savings. AWS Native has no native vuln remediation planning. Separate ServiceNow/JIRA workflows required. No migration-aware patch scheduling. [Ref: ServiceNow VR + AWS Native product scope]</t>
+          <t>53% savings (WEIGHTED: AWS-native 60% x 26% + Industry 50% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -2804,11 +2804,11 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>52% savings. AWS Native does not include patch management — requires separate SSM/Ansible. No auto-generated compliance evidence trail. [Ref: AWS SSM + AWS Native product scope]</t>
+          <t>55% savings (WEIGHTED: AWS-native 65% x 26% + Industry 52% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -2834,11 +2834,11 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>0.35</v>
+        <v>0.42</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>55% savings. AWS Native does not provide continuous vulnerability monitoring. Requires separate Nessus/Qualys scheduled scans + manual JIRA ticketing. [Ref: Industry avg + AWS Native product scope]</t>
+          <t>58% savings (WEIGHTED: AWS-native 65% x 26% + Industry 55% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -2857,6 +2857,8 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
@@ -8509,7 +8511,7 @@
         <v>71</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>16</v>
@@ -8556,7 +8558,7 @@
         <v>112</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>143</v>
+        <v>47</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>22</v>
@@ -8603,7 +8605,7 @@
         <v>92</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>117</v>
+        <v>39</v>
       </c>
       <c r="E37" s="7" t="n">
         <v>16</v>
@@ -8650,7 +8652,7 @@
         <v>46</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>17</v>
@@ -8697,7 +8699,7 @@
         <v>33</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>10</v>
@@ -8744,7 +8746,7 @@
         <v>58</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="E40" s="7" t="n">
         <v>11</v>
@@ -8791,7 +8793,7 @@
         <v>35</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>8</v>
@@ -8838,7 +8840,7 @@
         <v>23</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="E42" s="7" t="n">
         <v>7</v>
@@ -8885,7 +8887,7 @@
         <v>71</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>6</v>
@@ -8932,7 +8934,7 @@
         <v>54</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="E44" s="7" t="n">
         <v>10</v>

--- a/sample_data/AWS_Transform_Kiro.xlsx
+++ b/sample_data/AWS_Transform_Kiro.xlsx
@@ -2084,11 +2084,11 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.37</v>
+        <v>0.3</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>63% savings (WEIGHTED: AWS-native 70% x 26% + Industry 60% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
+          <t>70% savings. AWS Migration Hub + Application Discovery Service: agentless/agent-based. COVERAGE: AWS targets only (26% of PG&amp;E). Azure/AzLocal need separate Azure Migrate.</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -2114,11 +2114,11 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>58% savings (WEIGHTED: AWS-native 65% x 26% + Industry 55% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
+          <t>65% savings. AWS ADS agent-based dependency mapping. COVERAGE: AWS targets only. Azure/AzLocal need separate tooling.</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -2144,11 +2144,11 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.37</v>
+        <v>0.28</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>63% savings (WEIGHTED: AWS-native 72% x 26% + Industry 60% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
+          <t>72% savings. AWS SCT: best-in-class schema analysis. COVERAGE: AWS DB targets only. Azure DBs need Azure DMA.</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -2174,11 +2174,11 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.32</v>
+        <v>0.25</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>68% savings (WEIGHTED: AWS-native 75% x 26% + Industry 65% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
+          <t>75% savings. AWS CloudWatch: native metric collection. COVERAGE: AWS instances only. Azure needs Azure Monitor.</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -2204,11 +2204,11 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>51% savings (WEIGHTED: AWS-native 58% x 26% + Industry 48% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
+          <t>58% savings. AWS Security Hub + Config Rules. COVERAGE: AWS resources only. Azure needs Defender for Cloud.</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -2234,11 +2234,11 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>58% savings (WEIGHTED: AWS-native 65% x 26% + Industry 55% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
+          <t>65% savings. AWS License Manager + OLA program. COVERAGE: AWS BYOL only. Azure licensing separate.</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -2264,11 +2264,11 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>67% savings (WEIGHTED: AWS-native 72% x 26% + Industry 65% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
+          <t>72% savings. AWS Migration Evaluator (TSO Logic). COVERAGE: AWS TCO only. No Azure/AzLocal comparison.</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -2294,11 +2294,11 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>60% savings (WEIGHTED: AWS-native 65% x 26% + Industry 58% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
+          <t>65% savings. AWS Migration Hub Orchestrator. COVERAGE: AWS migrations only. Azure/AzLocal need separate orchestration.</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -2324,11 +2324,11 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.37</v>
+        <v>0.3</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>63% savings (WEIGHTED: AWS-native 70% x 26% + Industry 60% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
+          <t>70% savings. AWS Control Tower + LZ Accelerator. COVERAGE: AWS LZ only. PG&amp;E provides all LZs.</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -2354,11 +2354,11 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>62% savings (WEIGHTED: AWS-native 68% x 26% + Industry 60% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
+          <t>68% savings. Kiro IDE: Claude AI-powered HCL generation. COVERAGE: AWS CloudFormation/HCL. Azure ARM separate.</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -2384,11 +2384,11 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0.41</v>
+        <v>0.3</v>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>59% savings (WEIGHTED: AWS-native 70% x 26% + Industry 55% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
+          <t>70% savings. Amazon Q Developer + Kiro: AI containerization. COVERAGE: EKS/ECR. AKS needs separate tooling.</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -2414,11 +2414,11 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>50% savings (WEIGHTED: AWS-native 65% x 26% + Industry 45% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
+          <t>65% savings. Amazon Q Transform: agentic .NET/Java (4x faster). COVERAGE: Works for all clouds (code-level tool).</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -2444,11 +2444,11 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>48% savings (WEIGHTED: AWS-native 55% x 26% + Industry 45% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
+          <t>55% savings. Amazon Q Transform: automated refactoring. COVERAGE: Partially cloud-agnostic.</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -2474,11 +2474,11 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>61% savings (WEIGHTED: AWS-native 70% x 26% + Industry 58% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
+          <t>70% savings. AWS SCT: native auto-conversion. COVERAGE: AWS-targeted DBs only. Azure DBs need DMA.</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -2504,11 +2504,11 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>0.46</v>
+        <v>0.4</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>54% savings (WEIGHTED: AWS-native 60% x 26% + Industry 52% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
+          <t>60% savings. AWS Migration Hub Orchestrator. COVERAGE: AWS migrations only.</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -2534,11 +2534,11 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>0.38</v>
+        <v>0.28</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>62% savings (WEIGHTED: AWS-native 72% x 26% + Industry 58% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
+          <t>72% savings. AWS MGN: BEST-IN-CLASS rehost. COVERAGE: AWS EC2 targets only. Azure needs ASR.</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -2564,11 +2564,11 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>55% savings (WEIGHTED: AWS-native 62% x 26% + Industry 52% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
+          <t>62% savings. AWS MGN + SSM post-launch scripts. COVERAGE: AWS targets only.</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -2594,11 +2594,11 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>55% savings (WEIGHTED: AWS-native 65% x 26% + Industry 52% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
+          <t>65% savings. AWS CodePipeline + ECR + EKS. COVERAGE: EKS only. AKS needs separate pipeline.</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -2624,11 +2624,11 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>0.53</v>
+        <v>0.48</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>47% savings (WEIGHTED: AWS-native 52% x 26% + Industry 45% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
+          <t>52% savings. Kiro IDE: AI test generation from specs. COVERAGE: Cloud-agnostic (code-level).</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -2654,11 +2654,11 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>46% savings (WEIGHTED: AWS-native 48% x 26% + Industry 45% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
+          <t>48% savings. No AWS-native perf testing. Standard JMeter/Gatling. COVERAGE: Cloud-agnostic.</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -2684,11 +2684,11 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>71% savings (WEIGHTED: AWS-native 78% x 26% + Industry 68% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
+          <t>78% savings. AWS Compute Optimizer: best-in-class (80%+ accuracy). COVERAGE: AWS instances only. Azure Advisor separate.</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -2714,11 +2714,11 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>0.41</v>
+        <v>0.3</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>59% savings (WEIGHTED: AWS-native 70% x 26% + Industry 55% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
+          <t>70% savings. AWS CloudWatch: native dashboards + alarms. COVERAGE: AWS resources only. Azure Monitor separate.</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -2744,11 +2744,11 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>62% savings (WEIGHTED: AWS-native 67% x 26% + Industry 60% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
+          <t>67% savings. AWS Inspector: continuous scanning. COVERAGE: AWS ECR/EC2 only. Azure needs Defender.</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -2774,11 +2774,11 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>53% savings (WEIGHTED: AWS-native 60% x 26% + Industry 50% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
+          <t>60% savings. AWS Security Hub + SSM. COVERAGE: AWS resources only.</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -2804,11 +2804,11 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>55% savings (WEIGHTED: AWS-native 65% x 26% + Industry 52% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
+          <t>65% savings. AWS SSM Patch Manager: automated. COVERAGE: AWS EC2 only. Azure needs Update Manager.</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -2834,11 +2834,11 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>58% savings (WEIGHTED: AWS-native 65% x 26% + Industry 55% x 74%). AWS tools only cover 107 AWS apps; Azure/AzLocal use industry-standard tools.</t>
+          <t>65% savings. AWS Inspector continuous + Security Hub. COVERAGE: AWS only.</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -8511,7 +8511,7 @@
         <v>71</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>16</v>
@@ -8558,7 +8558,7 @@
         <v>112</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>22</v>
@@ -8605,7 +8605,7 @@
         <v>92</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E37" s="7" t="n">
         <v>16</v>
@@ -8652,7 +8652,7 @@
         <v>46</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>17</v>
@@ -8699,7 +8699,7 @@
         <v>33</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>10</v>
@@ -8746,7 +8746,7 @@
         <v>58</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E40" s="7" t="n">
         <v>11</v>
@@ -8793,7 +8793,7 @@
         <v>35</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>8</v>
@@ -8840,7 +8840,7 @@
         <v>23</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E42" s="7" t="n">
         <v>7</v>
@@ -8887,7 +8887,7 @@
         <v>71</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>6</v>
@@ -8934,7 +8934,7 @@
         <v>54</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E44" s="7" t="n">
         <v>10</v>

--- a/sample_data/AWS_Transform_Kiro.xlsx
+++ b/sample_data/AWS_Transform_Kiro.xlsx
@@ -2857,8 +2857,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
@@ -8374,8 +8372,6 @@
       </c>
       <c r="I29" s="15" t="n"/>
     </row>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
@@ -9008,8 +9004,6 @@
         <v/>
       </c>
     </row>
-    <row r="46"/>
-    <row r="47"/>
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>
@@ -12737,7 +12731,7 @@
         <v>181</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D14" s="22" t="n">
         <v>1050</v>
@@ -12754,7 +12748,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="22" t="n">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="I14" s="22">
         <f>E14+F14+G14+H14</f>
@@ -12771,7 +12765,7 @@
         <v>269</v>
       </c>
       <c r="C15" s="100" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D15" s="102" t="n">
         <v>1050</v>
@@ -12788,7 +12782,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="102" t="n">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="I15" s="102">
         <f>E15+F15+G15+H15</f>
@@ -12805,7 +12799,7 @@
         <v>305</v>
       </c>
       <c r="C16" s="100" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D16" s="102" t="n">
         <v>1050</v>
@@ -12822,7 +12816,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="102" t="n">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="I16" s="102">
         <f>E16+F16+G16+H16</f>
@@ -12885,7 +12879,7 @@
       <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="n"/>
       <c r="I20" s="103" t="n">
-        <v>10840125</v>
+        <v>10174500</v>
       </c>
     </row>
     <row r="21">

--- a/sample_data/AWS_Transform_Kiro.xlsx
+++ b/sample_data/AWS_Transform_Kiro.xlsx
@@ -8372,6 +8372,8 @@
       </c>
       <c r="I29" s="15" t="n"/>
     </row>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
@@ -8504,10 +8506,10 @@
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>16</v>
@@ -8551,10 +8553,10 @@
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>22</v>
@@ -8598,10 +8600,10 @@
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E37" s="7" t="n">
         <v>16</v>
@@ -8645,10 +8647,10 @@
         </is>
       </c>
       <c r="C38" s="7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>17</v>
@@ -8695,7 +8697,7 @@
         <v>33</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>10</v>
@@ -8739,10 +8741,10 @@
         </is>
       </c>
       <c r="C40" s="7" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E40" s="7" t="n">
         <v>11</v>
@@ -8789,7 +8791,7 @@
         <v>35</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>8</v>
@@ -8833,10 +8835,10 @@
         </is>
       </c>
       <c r="C42" s="7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E42" s="7" t="n">
         <v>7</v>
@@ -8880,10 +8882,10 @@
         </is>
       </c>
       <c r="C43" s="7" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>6</v>
@@ -8927,10 +8929,10 @@
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E44" s="7" t="n">
         <v>10</v>
@@ -9004,6 +9006,8 @@
         <v/>
       </c>
     </row>
+    <row r="46"/>
+    <row r="47"/>
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>

--- a/sample_data/AWS_Transform_Kiro.xlsx
+++ b/sample_data/AWS_Transform_Kiro.xlsx
@@ -8372,8 +8372,6 @@
       </c>
       <c r="I29" s="15" t="n"/>
     </row>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
@@ -9006,8 +9004,6 @@
         <v/>
       </c>
     </row>
-    <row r="46"/>
-    <row r="47"/>
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>
@@ -12735,7 +12731,7 @@
         <v>181</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" s="22" t="n">
         <v>1050</v>
@@ -12883,7 +12879,7 @@
       <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="n"/>
       <c r="I20" s="103" t="n">
-        <v>10174500</v>
+        <v>10894125</v>
       </c>
     </row>
     <row r="21">
